--- a/basedatos_partidas/salida/descompuestos/CT-07-01-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-01-030.xlsx
@@ -539,10 +539,10 @@
         <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.48</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -591,10 +591,10 @@
         <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="H12" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="13">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.17</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>12.52</v>
+        <v>10.86</v>
       </c>
       <c r="H25" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>12.65</v>
+        <v>10.97</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-07-01-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-01-030.xlsx
@@ -522,7 +522,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-MOR-FRISO</t>
+          <t>MT-CEMENTO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -532,95 +532,95 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Mortero de friso para revestimiento de paramentos, elaborado con cemento y arena cernida.</t>
+          <t>Cemento Portland gris tipo I, en saco. Para mortero de friso.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>11.9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.225</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-HIDROFUGO</t>
+          <t>MT-ARENA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Aditivo hidrófugo de masa para morteros de friso en exteriores y áreas húmedas.</t>
+          <t>Arena lavada de río, puesta en obra, para camas de asiento y rellenos de zanja. Para mortero de friso.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.45</v>
+        <v>0.0294</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>1.89</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-CEMENTO</t>
+          <t>MT-AGUA-OBRA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Cemento Portland gris tipo I, en saco.</t>
+          <t>Agua para amasado, humectación de rellenos y compactación. Para mortero de friso.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>0.02416</v>
       </c>
       <c r="G12" t="n">
-        <v>0.225</v>
+        <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.79</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MT-AGUA-OBRA</t>
+          <t>MT-HIDROFUGO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>l</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Agua para amasado, humectación de rellenos y compactación.</t>
+          <t>Aditivo hidrófugo de masa para morteros de friso en exteriores y áreas húmedas.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.018</v>
+        <v>0.45</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.03</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.51</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="15">
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>10.86</v>
+        <v>10.61</v>
       </c>
       <c r="H25" t="n">
         <v>0.11</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>10.97</v>
+        <v>10.72</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-07-01-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-07-01-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 07 Frisos y revestimientos de pared</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Frisos y enlucidos de mortero</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
